--- a/public/Empleados faltantes.xlsx
+++ b/public/Empleados faltantes.xlsx
@@ -1820,7 +1820,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>6224</v>
+        <v>6204</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>37</v>
